--- a/data/la_colorada.xlsx
+++ b/data/la_colorada.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,30 +457,45 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>05dec2025</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>06dec2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>07dec2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -505,21 +520,30 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>7</v>
       </c>
-      <c r="G2" t="n">
+      <c r="J2" t="n">
         <v>13</v>
       </c>
-      <c r="H2" t="n">
+      <c r="K2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="n">
+      <c r="L2" t="n">
         <v>14</v>
       </c>
-      <c r="J2" t="n">
+      <c r="M2" t="n">
         <v>17</v>
       </c>
-      <c r="K2" t="n">
+      <c r="N2" t="n">
         <v>21</v>
       </c>
     </row>
@@ -542,21 +566,30 @@
         <v>8</v>
       </c>
       <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>5</v>
-      </c>
-      <c r="G3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H3" t="n">
-        <v>15</v>
-      </c>
-      <c r="I3" t="n">
-        <v>17</v>
       </c>
       <c r="J3" t="n">
         <v>10</v>
       </c>
       <c r="K3" t="n">
+        <v>15</v>
+      </c>
+      <c r="L3" t="n">
+        <v>17</v>
+      </c>
+      <c r="M3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -579,21 +612,30 @@
         <v>10</v>
       </c>
       <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>5</v>
       </c>
-      <c r="G4" t="n">
+      <c r="J4" t="n">
         <v>14</v>
       </c>
-      <c r="H4" t="n">
+      <c r="K4" t="n">
         <v>15</v>
       </c>
-      <c r="I4" t="n">
+      <c r="L4" t="n">
         <v>15</v>
       </c>
-      <c r="J4" t="n">
+      <c r="M4" t="n">
         <v>20</v>
       </c>
-      <c r="K4" t="n">
+      <c r="N4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -616,21 +658,30 @@
         <v>21</v>
       </c>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>26</v>
+      </c>
+      <c r="I5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" t="n">
+      <c r="J5" t="n">
         <v>14</v>
       </c>
-      <c r="H5" t="n">
+      <c r="K5" t="n">
         <v>14</v>
       </c>
-      <c r="I5" t="n">
+      <c r="L5" t="n">
         <v>20</v>
       </c>
-      <c r="J5" t="n">
+      <c r="M5" t="n">
         <v>24</v>
       </c>
-      <c r="K5" t="n">
+      <c r="N5" t="n">
         <v>28</v>
       </c>
     </row>
@@ -653,21 +704,30 @@
         <v>7</v>
       </c>
       <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>9</v>
+      </c>
+      <c r="I6" t="n">
         <v>7</v>
       </c>
-      <c r="G6" t="n">
+      <c r="J6" t="n">
         <v>9</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>21</v>
       </c>
-      <c r="J6" t="n">
+      <c r="M6" t="n">
         <v>15</v>
       </c>
-      <c r="K6" t="n">
+      <c r="N6" t="n">
         <v>25</v>
       </c>
     </row>
@@ -690,21 +750,30 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
         <v>5</v>
       </c>
-      <c r="G7" t="n">
+      <c r="J7" t="n">
         <v>14</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>37</v>
       </c>
-      <c r="J7" t="n">
+      <c r="M7" t="n">
         <v>25</v>
       </c>
-      <c r="K7" t="n">
+      <c r="N7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -727,21 +796,30 @@
         <v>3</v>
       </c>
       <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="n">
         <v>12</v>
       </c>
-      <c r="H8" t="n">
+      <c r="K8" t="n">
         <v>16</v>
       </c>
-      <c r="I8" t="n">
+      <c r="L8" t="n">
         <v>15</v>
       </c>
-      <c r="J8" t="n">
+      <c r="M8" t="n">
         <v>10</v>
       </c>
-      <c r="K8" t="n">
+      <c r="N8" t="n">
         <v>18</v>
       </c>
     </row>
@@ -764,21 +842,30 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
         <v>7</v>
       </c>
-      <c r="G9" t="n">
+      <c r="J9" t="n">
         <v>13</v>
       </c>
-      <c r="H9" t="n">
+      <c r="K9" t="n">
         <v>22</v>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>18</v>
       </c>
-      <c r="K9" t="n">
+      <c r="N9" t="n">
         <v>21</v>
       </c>
     </row>
@@ -804,18 +891,27 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
         <v>10</v>
       </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -838,21 +934,30 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
         <v>8</v>
       </c>
-      <c r="G11" t="n">
+      <c r="J11" t="n">
         <v>14</v>
       </c>
-      <c r="H11" t="n">
+      <c r="K11" t="n">
         <v>17</v>
       </c>
-      <c r="I11" t="n">
+      <c r="L11" t="n">
         <v>17</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>16</v>
       </c>
     </row>
@@ -875,21 +980,30 @@
         <v>8</v>
       </c>
       <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="n">
         <v>3</v>
-      </c>
-      <c r="G12" t="n">
-        <v>11</v>
-      </c>
-      <c r="H12" t="n">
-        <v>15</v>
-      </c>
-      <c r="I12" t="n">
-        <v>16</v>
       </c>
       <c r="J12" t="n">
         <v>11</v>
       </c>
       <c r="K12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L12" t="n">
+        <v>16</v>
+      </c>
+      <c r="M12" t="n">
+        <v>11</v>
+      </c>
+      <c r="N12" t="n">
         <v>17</v>
       </c>
     </row>
@@ -912,21 +1026,30 @@
         <v>12</v>
       </c>
       <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
         <v>5</v>
       </c>
-      <c r="G13" t="n">
+      <c r="J13" t="n">
         <v>10</v>
       </c>
-      <c r="H13" t="n">
+      <c r="K13" t="n">
         <v>17</v>
       </c>
-      <c r="I13" t="n">
+      <c r="L13" t="n">
         <v>15</v>
       </c>
-      <c r="J13" t="n">
+      <c r="M13" t="n">
         <v>20</v>
       </c>
-      <c r="K13" t="n">
+      <c r="N13" t="n">
         <v>20</v>
       </c>
     </row>
@@ -949,21 +1072,30 @@
         <v>3</v>
       </c>
       <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
         <v>2</v>
       </c>
-      <c r="G14" t="n">
-        <v>11</v>
-      </c>
       <c r="H14" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>11</v>
       </c>
       <c r="K14" t="n">
+        <v>27</v>
+      </c>
+      <c r="L14" t="n">
+        <v>16</v>
+      </c>
+      <c r="M14" t="n">
+        <v>11</v>
+      </c>
+      <c r="N14" t="n">
         <v>13</v>
       </c>
     </row>
@@ -986,21 +1118,30 @@
         <v>7</v>
       </c>
       <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>6</v>
+      </c>
+      <c r="I15" t="n">
         <v>3</v>
       </c>
-      <c r="G15" t="n">
+      <c r="J15" t="n">
         <v>14</v>
       </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>18</v>
       </c>
-      <c r="J15" t="n">
+      <c r="M15" t="n">
         <v>15</v>
       </c>
-      <c r="K15" t="n">
+      <c r="N15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1015,7 +1156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1046,30 +1187,45 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>05dec2025</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>06dec2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>07dec2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1099,30 +1255,41 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1156,30 +1323,37 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1209,30 +1383,41 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -1260,32 +1445,43 @@
           <t>21</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -1319,26 +1515,41 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -1362,28 +1573,35 @@
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1411,32 +1629,43 @@
           <t>3</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1460,28 +1689,35 @@
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1498,15 +1734,18 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1526,28 +1765,31 @@
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1575,32 +1817,43 @@
           <t>8</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -1628,32 +1881,39 @@
           <t>12</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -1685,32 +1945,39 @@
           <t>3</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -1742,28 +2009,35 @@
           <t>7</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/la_colorada.xlsx
+++ b/data/la_colorada.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,30 +472,40 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>08dec2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>09dec2025</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -529,21 +539,27 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>7</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>13</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>14</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>17</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>21</v>
       </c>
     </row>
@@ -575,21 +591,27 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>5</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>10</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>15</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>17</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -621,21 +643,27 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
         <v>5</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L4" t="n">
         <v>14</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>15</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>15</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>20</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -667,21 +695,27 @@
         <v>26</v>
       </c>
       <c r="I5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>4</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>14</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>14</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>20</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>24</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>28</v>
       </c>
     </row>
@@ -713,21 +747,27 @@
         <v>9</v>
       </c>
       <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>18</v>
+      </c>
+      <c r="K6" t="n">
         <v>7</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>9</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>21</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>15</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>25</v>
       </c>
     </row>
@@ -759,21 +799,27 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>5</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>14</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>37</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>25</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -805,21 +851,27 @@
         <v>2</v>
       </c>
       <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" t="n">
         <v>2</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>12</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>16</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>15</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>10</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>18</v>
       </c>
     </row>
@@ -851,21 +903,27 @@
         <v>4</v>
       </c>
       <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>9</v>
+      </c>
+      <c r="K9" t="n">
         <v>7</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>13</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>22</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
         <v>18</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>21</v>
       </c>
     </row>
@@ -900,18 +958,24 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>10</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -943,21 +1007,27 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>8</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>14</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>17</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
         <v>17</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
         <v>16</v>
       </c>
     </row>
@@ -989,21 +1059,27 @@
         <v>2</v>
       </c>
       <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>3</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>11</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>15</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>16</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>11</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1035,21 +1111,27 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>18</v>
+      </c>
+      <c r="K13" t="n">
         <v>5</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>10</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>17</v>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
         <v>15</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>20</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1081,21 +1163,27 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>2</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>11</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>27</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>16</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>11</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1127,21 +1215,27 @@
         <v>6</v>
       </c>
       <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>3</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>14</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>18</v>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>15</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1156,7 +1250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1202,30 +1296,40 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>08dec2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>09dec2025</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1266,30 +1370,36 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1330,30 +1440,36 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1392,32 +1508,38 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -1458,30 +1580,36 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -1528,28 +1656,34 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -1582,26 +1716,32 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1642,30 +1782,40 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1698,26 +1848,36 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1737,15 +1897,17 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1770,26 +1932,32 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1828,32 +1996,34 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -1888,32 +2058,38 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -1954,30 +2130,36 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -2016,28 +2198,30 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/la_colorada.xlsx
+++ b/data/la_colorada.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,30 +482,35 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>10dec2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -545,21 +550,24 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L2" t="n">
         <v>7</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>13</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>1</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>14</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>17</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>21</v>
       </c>
     </row>
@@ -597,21 +605,24 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>5</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>10</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>15</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>17</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>10</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -649,23 +660,26 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>14</v>
-      </c>
-      <c r="M4" t="n">
-        <v>15</v>
       </c>
       <c r="N4" t="n">
         <v>15</v>
       </c>
       <c r="O4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="P4" t="n">
         <v>20</v>
       </c>
+      <c r="Q4" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -701,21 +715,24 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
+        <v>19</v>
+      </c>
+      <c r="L5" t="n">
         <v>4</v>
-      </c>
-      <c r="L5" t="n">
-        <v>14</v>
       </c>
       <c r="M5" t="n">
         <v>14</v>
       </c>
       <c r="N5" t="n">
+        <v>14</v>
+      </c>
+      <c r="O5" t="n">
         <v>20</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>24</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>28</v>
       </c>
     </row>
@@ -753,21 +770,24 @@
         <v>18</v>
       </c>
       <c r="K6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" t="n">
         <v>7</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>9</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
       <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
         <v>21</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>15</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>25</v>
       </c>
     </row>
@@ -805,21 +825,24 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
+        <v>11</v>
+      </c>
+      <c r="L7" t="n">
         <v>5</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>14</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
         <v>37</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>25</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -857,21 +880,24 @@
         <v>5</v>
       </c>
       <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>2</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>12</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>16</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>15</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>18</v>
       </c>
     </row>
@@ -909,21 +935,24 @@
         <v>9</v>
       </c>
       <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="n">
         <v>7</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>13</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>22</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
       <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
         <v>18</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>21</v>
       </c>
     </row>
@@ -964,11 +993,11 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>10</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
@@ -976,6 +1005,9 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1013,21 +1045,24 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
+        <v>5</v>
+      </c>
+      <c r="L11" t="n">
         <v>8</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>14</v>
-      </c>
-      <c r="M11" t="n">
-        <v>17</v>
       </c>
       <c r="N11" t="n">
         <v>17</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>16</v>
       </c>
     </row>
@@ -1065,21 +1100,24 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
+        <v>18</v>
+      </c>
+      <c r="L12" t="n">
         <v>3</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>11</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>15</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>16</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>11</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1117,23 +1155,26 @@
         <v>18</v>
       </c>
       <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>5</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>10</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>17</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>15</v>
-      </c>
-      <c r="O13" t="n">
-        <v>20</v>
       </c>
       <c r="P13" t="n">
         <v>20</v>
       </c>
+      <c r="Q13" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1169,21 +1210,24 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
+        <v>9</v>
+      </c>
+      <c r="L14" t="n">
         <v>2</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>11</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>27</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>16</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>11</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1221,21 +1265,24 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>14</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
       <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>18</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>15</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1250,7 +1297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1306,30 +1353,35 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>10dec2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1376,30 +1428,35 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1444,32 +1501,33 @@
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1516,30 +1574,35 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -1586,30 +1649,35 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -1664,26 +1732,31 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -1722,26 +1795,31 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1790,32 +1868,33 @@
           <t>5</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1858,26 +1937,31 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1899,15 +1983,16 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1938,26 +2023,31 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -2000,30 +2090,35 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -2064,32 +2159,33 @@
           <t>18</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -2136,30 +2232,35 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -2200,28 +2301,29 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/la_colorada.xlsx
+++ b/data/la_colorada.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,30 +487,35 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>11dec2025</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -553,21 +558,24 @@
         <v>8</v>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>7</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>13</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>1</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>14</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>17</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>21</v>
       </c>
     </row>
@@ -608,21 +616,24 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>15</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>17</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>10</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -663,23 +674,26 @@
         <v>9</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>5</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>14</v>
-      </c>
-      <c r="N4" t="n">
-        <v>15</v>
       </c>
       <c r="O4" t="n">
         <v>15</v>
       </c>
       <c r="P4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Q4" t="n">
         <v>20</v>
       </c>
+      <c r="R4" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -718,21 +732,24 @@
         <v>19</v>
       </c>
       <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
         <v>4</v>
-      </c>
-      <c r="M5" t="n">
-        <v>14</v>
       </c>
       <c r="N5" t="n">
         <v>14</v>
       </c>
       <c r="O5" t="n">
+        <v>14</v>
+      </c>
+      <c r="P5" t="n">
         <v>20</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>24</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>28</v>
       </c>
     </row>
@@ -773,21 +790,24 @@
         <v>8</v>
       </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>9</v>
       </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
       <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
         <v>21</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>15</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>25</v>
       </c>
     </row>
@@ -828,21 +848,24 @@
         <v>11</v>
       </c>
       <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
         <v>5</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>14</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
       <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>37</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>25</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -883,21 +906,24 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>12</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>16</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>15</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>10</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>18</v>
       </c>
     </row>
@@ -938,21 +964,24 @@
         <v>2</v>
       </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>7</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>13</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>22</v>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
       <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>18</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>21</v>
       </c>
     </row>
@@ -996,11 +1025,11 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>10</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
@@ -1008,6 +1037,9 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1048,21 +1080,24 @@
         <v>5</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>8</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>14</v>
-      </c>
-      <c r="N11" t="n">
-        <v>17</v>
       </c>
       <c r="O11" t="n">
         <v>17</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
         <v>16</v>
       </c>
     </row>
@@ -1103,21 +1138,24 @@
         <v>18</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>3</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>11</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>15</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>16</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>11</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1158,23 +1196,26 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
         <v>5</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>10</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>17</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>15</v>
-      </c>
-      <c r="P13" t="n">
-        <v>20</v>
       </c>
       <c r="Q13" t="n">
         <v>20</v>
       </c>
+      <c r="R13" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1213,21 +1254,24 @@
         <v>9</v>
       </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>2</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>11</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>27</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>16</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>11</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1268,21 +1312,24 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>3</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>14</v>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
       <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
         <v>18</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>15</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1297,7 +1344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1358,30 +1405,35 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>11dec2025</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1431,32 +1483,33 @@
           <t>8</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1502,32 +1555,33 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1577,32 +1631,33 @@
           <t>9</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -1654,30 +1709,35 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -1735,28 +1795,29 @@
           <t>8</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -1800,26 +1861,31 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1869,32 +1935,33 @@
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1940,28 +2007,29 @@
           <t>2</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1984,15 +2052,16 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -2026,28 +2095,29 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -2093,32 +2163,33 @@
           <t>18</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -2162,30 +2233,35 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -2235,32 +2311,33 @@
           <t>9</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -2302,28 +2379,29 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/la_colorada.xlsx
+++ b/data/la_colorada.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,30 +492,45 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>12dec2025</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>13dec2025</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14dec2025</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -561,21 +576,30 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>7</v>
       </c>
-      <c r="N2" t="n">
+      <c r="Q2" t="n">
         <v>13</v>
       </c>
-      <c r="O2" t="n">
+      <c r="R2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" t="n">
+      <c r="S2" t="n">
         <v>14</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="T2" t="n">
         <v>17</v>
       </c>
-      <c r="R2" t="n">
+      <c r="U2" t="n">
         <v>21</v>
       </c>
     </row>
@@ -619,21 +643,30 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
         <v>5</v>
-      </c>
-      <c r="N3" t="n">
-        <v>10</v>
-      </c>
-      <c r="O3" t="n">
-        <v>15</v>
-      </c>
-      <c r="P3" t="n">
-        <v>17</v>
       </c>
       <c r="Q3" t="n">
         <v>10</v>
       </c>
       <c r="R3" t="n">
+        <v>15</v>
+      </c>
+      <c r="S3" t="n">
+        <v>17</v>
+      </c>
+      <c r="T3" t="n">
+        <v>10</v>
+      </c>
+      <c r="U3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -677,21 +710,30 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
         <v>5</v>
       </c>
-      <c r="N4" t="n">
+      <c r="Q4" t="n">
         <v>14</v>
       </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
         <v>15</v>
       </c>
-      <c r="P4" t="n">
+      <c r="S4" t="n">
         <v>15</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="T4" t="n">
         <v>20</v>
       </c>
-      <c r="R4" t="n">
+      <c r="U4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -735,21 +777,30 @@
         <v>3</v>
       </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>4</v>
       </c>
-      <c r="N5" t="n">
+      <c r="Q5" t="n">
         <v>14</v>
       </c>
-      <c r="O5" t="n">
+      <c r="R5" t="n">
         <v>14</v>
       </c>
-      <c r="P5" t="n">
+      <c r="S5" t="n">
         <v>20</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="T5" t="n">
         <v>24</v>
       </c>
-      <c r="R5" t="n">
+      <c r="U5" t="n">
         <v>28</v>
       </c>
     </row>
@@ -793,21 +844,30 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
         <v>7</v>
       </c>
-      <c r="N6" t="n">
+      <c r="Q6" t="n">
         <v>9</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>21</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="T6" t="n">
         <v>15</v>
       </c>
-      <c r="R6" t="n">
+      <c r="U6" t="n">
         <v>25</v>
       </c>
     </row>
@@ -851,21 +911,30 @@
         <v>1</v>
       </c>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>5</v>
       </c>
-      <c r="N7" t="n">
+      <c r="Q7" t="n">
         <v>14</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>37</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="T7" t="n">
         <v>25</v>
       </c>
-      <c r="R7" t="n">
+      <c r="U7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -912,18 +981,27 @@
         <v>2</v>
       </c>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="n">
         <v>12</v>
       </c>
-      <c r="O8" t="n">
+      <c r="R8" t="n">
         <v>16</v>
       </c>
-      <c r="P8" t="n">
+      <c r="S8" t="n">
         <v>15</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="T8" t="n">
         <v>10</v>
       </c>
-      <c r="R8" t="n">
+      <c r="U8" t="n">
         <v>18</v>
       </c>
     </row>
@@ -967,21 +1045,30 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
         <v>7</v>
       </c>
-      <c r="N9" t="n">
+      <c r="Q9" t="n">
         <v>13</v>
       </c>
-      <c r="O9" t="n">
+      <c r="R9" t="n">
         <v>22</v>
       </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
         <v>18</v>
       </c>
-      <c r="R9" t="n">
+      <c r="U9" t="n">
         <v>21</v>
       </c>
     </row>
@@ -1028,18 +1115,27 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>10</v>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1083,21 +1179,30 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3</v>
+      </c>
+      <c r="P11" t="n">
         <v>8</v>
       </c>
-      <c r="N11" t="n">
+      <c r="Q11" t="n">
         <v>14</v>
       </c>
-      <c r="O11" t="n">
+      <c r="R11" t="n">
         <v>17</v>
       </c>
-      <c r="P11" t="n">
+      <c r="S11" t="n">
         <v>17</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
         <v>16</v>
       </c>
     </row>
@@ -1141,21 +1246,30 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
         <v>3</v>
-      </c>
-      <c r="N12" t="n">
-        <v>11</v>
-      </c>
-      <c r="O12" t="n">
-        <v>15</v>
-      </c>
-      <c r="P12" t="n">
-        <v>16</v>
       </c>
       <c r="Q12" t="n">
         <v>11</v>
       </c>
       <c r="R12" t="n">
+        <v>15</v>
+      </c>
+      <c r="S12" t="n">
+        <v>16</v>
+      </c>
+      <c r="T12" t="n">
+        <v>11</v>
+      </c>
+      <c r="U12" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1199,21 +1313,30 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
         <v>5</v>
       </c>
-      <c r="N13" t="n">
+      <c r="Q13" t="n">
         <v>10</v>
       </c>
-      <c r="O13" t="n">
+      <c r="R13" t="n">
         <v>17</v>
       </c>
-      <c r="P13" t="n">
+      <c r="S13" t="n">
         <v>15</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="T13" t="n">
         <v>20</v>
       </c>
-      <c r="R13" t="n">
+      <c r="U13" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1257,21 +1380,30 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>2</v>
-      </c>
-      <c r="N14" t="n">
-        <v>11</v>
-      </c>
-      <c r="O14" t="n">
-        <v>27</v>
-      </c>
-      <c r="P14" t="n">
-        <v>16</v>
       </c>
       <c r="Q14" t="n">
         <v>11</v>
       </c>
       <c r="R14" t="n">
+        <v>27</v>
+      </c>
+      <c r="S14" t="n">
+        <v>16</v>
+      </c>
+      <c r="T14" t="n">
+        <v>11</v>
+      </c>
+      <c r="U14" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1315,21 +1447,30 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>5</v>
+      </c>
+      <c r="P15" t="n">
         <v>3</v>
       </c>
-      <c r="N15" t="n">
+      <c r="Q15" t="n">
         <v>14</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>18</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="T15" t="n">
         <v>15</v>
       </c>
-      <c r="R15" t="n">
+      <c r="U15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1344,7 +1485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1410,30 +1551,45 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>12dec2025</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>13dec2025</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14dec2025</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1486,30 +1642,41 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1556,32 +1723,35 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1632,32 +1802,39 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -1712,32 +1889,35 @@
           <t>3</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -1796,28 +1976,31 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -1864,28 +2047,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1941,27 +2127,38 @@
           <t>2</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -2008,28 +2205,31 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -2053,15 +2253,18 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -2096,28 +2299,35 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -2166,30 +2376,37 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -2236,32 +2453,35 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -2312,32 +2532,35 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -2380,28 +2603,35 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
